--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEBRASKA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEBRASKA_2012.xlsx
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C135">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C754">
